--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4749"/>
+  <dimension ref="A1:B4752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47920,6 +47920,36 @@
         <v>0.9</v>
       </c>
     </row>
+    <row r="4750">
+      <c r="A4750" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B4750" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="4751">
+      <c r="A4751" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B4751" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="4752">
+      <c r="A4752" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B4752" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4752"/>
+  <dimension ref="A1:B4754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47950,6 +47950,26 @@
         <v>0.93</v>
       </c>
     </row>
+    <row r="4753">
+      <c r="A4753" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B4753" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="4754">
+      <c r="A4754" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B4754" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4754"/>
+  <dimension ref="A1:B4756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47970,6 +47970,26 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="4755">
+      <c r="A4755" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B4755" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="4756">
+      <c r="A4756" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B4756" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4756"/>
+  <dimension ref="A1:B4759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47990,6 +47990,36 @@
         <v>0.93</v>
       </c>
     </row>
+    <row r="4757">
+      <c r="A4757" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B4757" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="4758">
+      <c r="A4758" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4758" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="4759">
+      <c r="A4759" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B4759" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4759"/>
+  <dimension ref="A1:B4761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48020,6 +48020,26 @@
         <v>0.93</v>
       </c>
     </row>
+    <row r="4760">
+      <c r="A4760" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B4760" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="4761">
+      <c r="A4761" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B4761" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4761"/>
+  <dimension ref="A1:B4765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48040,6 +48040,46 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="4762">
+      <c r="A4762" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B4762" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="4763">
+      <c r="A4763" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B4763" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="4764">
+      <c r="A4764" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B4764" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="4765">
+      <c r="A4765" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B4765" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4765"/>
+  <dimension ref="A1:B4769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48080,6 +48080,46 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="4766">
+      <c r="A4766" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B4766" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="4767">
+      <c r="A4767" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B4767" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="4768">
+      <c r="A4768" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B4768" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="4769">
+      <c r="A4769" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B4769" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4769"/>
+  <dimension ref="A1:B4770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48120,6 +48120,16 @@
         <v>0.92</v>
       </c>
     </row>
+    <row r="4770">
+      <c r="A4770" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B4770" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4770"/>
+  <dimension ref="A1:B4775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48130,6 +48130,56 @@
         <v>0.92</v>
       </c>
     </row>
+    <row r="4771">
+      <c r="A4771" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B4771" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="4772">
+      <c r="A4772" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B4772" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="4773">
+      <c r="A4773" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B4773" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4774">
+      <c r="A4774" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B4774" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="4775">
+      <c r="A4775" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B4775" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4775"/>
+  <dimension ref="A1:B4776"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48180,6 +48180,16 @@
         <v>0.9399999999999999</v>
       </c>
     </row>
+    <row r="4776">
+      <c r="A4776" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B4776" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4776"/>
+  <dimension ref="A1:B4777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48190,6 +48190,16 @@
         <v>0.93</v>
       </c>
     </row>
+    <row r="4777">
+      <c r="A4777" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B4777" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4777"/>
+  <dimension ref="A1:B4780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48200,6 +48200,36 @@
         <v>0.89</v>
       </c>
     </row>
+    <row r="4778">
+      <c r="A4778" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B4778" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="4779">
+      <c r="A4779" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B4779" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="4780">
+      <c r="A4780" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B4780" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4780"/>
+  <dimension ref="A1:B4782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48230,6 +48230,26 @@
         <v>0.82</v>
       </c>
     </row>
+    <row r="4781">
+      <c r="A4781" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B4781" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="4782">
+      <c r="A4782" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B4782" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4782"/>
+  <dimension ref="A1:B4783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48250,6 +48250,16 @@
         <v>0.8100000000000001</v>
       </c>
     </row>
+    <row r="4783">
+      <c r="A4783" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B4783" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4783"/>
+  <dimension ref="A1:B4784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48260,6 +48260,16 @@
         <v>0.78</v>
       </c>
     </row>
+    <row r="4784">
+      <c r="A4784" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B4784" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4784"/>
+  <dimension ref="A1:B4788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48270,6 +48270,46 @@
         <v>0.7</v>
       </c>
     </row>
+    <row r="4785">
+      <c r="A4785" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B4785" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="4786">
+      <c r="A4786" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B4786" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="4787">
+      <c r="A4787" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B4787" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="4788">
+      <c r="A4788" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B4788" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4788"/>
+  <dimension ref="A1:B4789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48310,6 +48310,16 @@
         <v>0.77</v>
       </c>
     </row>
+    <row r="4789">
+      <c r="A4789" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B4789" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4789"/>
+  <dimension ref="A1:B4793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48320,6 +48320,46 @@
         <v>0.76</v>
       </c>
     </row>
+    <row r="4790">
+      <c r="A4790" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B4790" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="4791">
+      <c r="A4791" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B4791" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="4792">
+      <c r="A4792" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B4792" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="4793">
+      <c r="A4793" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B4793" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4793"/>
+  <dimension ref="A1:B4797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48360,6 +48360,46 @@
         <v>0.78</v>
       </c>
     </row>
+    <row r="4794">
+      <c r="A4794" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B4794" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="4795">
+      <c r="A4795" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B4795" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="4796">
+      <c r="A4796" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B4796" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="4797">
+      <c r="A4797" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B4797" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4797"/>
+  <dimension ref="A1:B4798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48400,6 +48400,16 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="4798">
+      <c r="A4798" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B4798" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4798"/>
+  <dimension ref="A1:B4801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48410,6 +48410,36 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="4799">
+      <c r="A4799" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B4799" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="4800">
+      <c r="A4800" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B4800" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="4801">
+      <c r="A4801" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B4801" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4801"/>
+  <dimension ref="A1:B4803"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48440,6 +48440,26 @@
         <v>0.77</v>
       </c>
     </row>
+    <row r="4802">
+      <c r="A4802" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B4802" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="4803">
+      <c r="A4803" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B4803" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4803"/>
+  <dimension ref="A1:B4804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48460,6 +48460,16 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="4804">
+      <c r="A4804" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B4804" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4804"/>
+  <dimension ref="A1:B4805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48470,6 +48470,16 @@
         <v>0.78</v>
       </c>
     </row>
+    <row r="4805">
+      <c r="A4805" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B4805" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4805"/>
+  <dimension ref="A1:B4807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48480,6 +48480,26 @@
         <v>0.77</v>
       </c>
     </row>
+    <row r="4806">
+      <c r="A4806" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B4806" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="4807">
+      <c r="A4807" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B4807" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4807"/>
+  <dimension ref="A1:B4812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48500,6 +48500,56 @@
         <v>0.77</v>
       </c>
     </row>
+    <row r="4808">
+      <c r="A4808" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B4808" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="4809">
+      <c r="A4809" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B4809" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="4810">
+      <c r="A4810" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B4810" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="4811">
+      <c r="A4811" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B4811" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="4812">
+      <c r="A4812" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B4812" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4812"/>
+  <dimension ref="A1:B4814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48550,6 +48550,26 @@
         <v>0.82</v>
       </c>
     </row>
+    <row r="4813">
+      <c r="A4813" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B4813" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="4814">
+      <c r="A4814" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B4814" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4814"/>
+  <dimension ref="A1:B4821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48570,6 +48570,76 @@
         <v>0.78</v>
       </c>
     </row>
+    <row r="4815">
+      <c r="A4815" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B4815" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="4816">
+      <c r="A4816" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B4816" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4817">
+      <c r="A4817" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B4817" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="4818">
+      <c r="A4818" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B4818" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="4819">
+      <c r="A4819" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B4819" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="4820">
+      <c r="A4820" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B4820" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="4821">
+      <c r="A4821" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B4821" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_sth.xlsx
+++ b/data_cripto/btc_mvrvz_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4821"/>
+  <dimension ref="A1:B4825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48640,6 +48640,46 @@
         <v>0.83</v>
       </c>
     </row>
+    <row r="4822">
+      <c r="A4822" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B4822" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="4823">
+      <c r="A4823" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B4823" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="4824">
+      <c r="A4824" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B4824" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="4825">
+      <c r="A4825" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B4825" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
